--- a/resources/topic/银行从业中级银行管理_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业中级银行管理_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rfa7b18a037fa4858"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="Ra8d621d35afb438f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R63f44950d98948db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rbb48af9ff76d4fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R9bbbc090acf446c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rf6728b725cd749dd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -65453,7 +65453,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-12 01:06:04+08:00（本地时间）</x:v>
+        <x:v>2026-09-12 07:05:50+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
